--- a/OUTPUT/direct_Q883X4_Pseudomonas_syringae_pv__tomato_str__DC3000.xlsx
+++ b/OUTPUT/direct_Q883X4_Pseudomonas_syringae_pv__tomato_str__DC3000.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1126</v>
+        <v>0.1127548980407837</v>
       </c>
     </row>
   </sheetData>
